--- a/src/assets/daily-template.xlsx
+++ b/src/assets/daily-template.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>تقرير مبيعات المعارض اليومي</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>كود المعرض</t>
-  </si>
-  <si>
-    <t>FW430</t>
   </si>
   <si>
     <t>مشرف المعرض</t>
@@ -1068,41 +1065,39 @@
       <c r="C2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>3</v>
-      </c>
+      <c r="D2" s="10"/>
       <c r="E2" s="11"/>
     </row>
     <row r="3" ht="49.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>7</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="17"/>
     </row>
     <row r="5" ht="51.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>10</v>
       </c>
       <c r="C5" s="20"/>
       <c r="D5" s="21"/>
@@ -1111,7 +1106,7 @@
     <row r="6" ht="51.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
       <c r="B6" s="24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
@@ -1120,7 +1115,7 @@
     <row r="7" ht="51.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="28"/>
       <c r="B7" s="29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="31"/>
@@ -1128,22 +1123,22 @@
     </row>
     <row r="8" ht="51.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="33"/>
       <c r="E8" s="22"/>
       <c r="H8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" ht="51.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="25"/>
       <c r="D9" s="26"/>
@@ -1152,30 +1147,30 @@
     <row r="10" ht="51.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="28"/>
       <c r="B10" s="29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="31"/>
       <c r="E10" s="32"/>
       <c r="J10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" ht="47.25" customHeight="1" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="C11" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="D11" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="E11" s="35" t="s">
         <v>19</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>20</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="36"/>

--- a/src/assets/daily-template.xlsx
+++ b/src/assets/daily-template.xlsx
@@ -88,61 +88,53 @@
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <charset val="178"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="12"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="18"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <family val="1"/>
-      <scheme val="major"/>
       <sz val="14"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <family val="1"/>
-      <scheme val="major"/>
       <sz val="14"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <family val="1"/>
-      <scheme val="major"/>
       <sz val="22"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <family val="1"/>
-      <scheme val="major"/>
       <sz val="16"/>
       <name val="Cambria"/>
     </font>
     <font>
       <b/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="16"/>
       <name val="Calibri"/>
     </font>
@@ -150,14 +142,12 @@
       <b/>
       <charset val="178"/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="14"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="22"/>
       <name val="Calibri"/>
     </font>
@@ -165,7 +155,6 @@
       <b/>
       <charset val="178"/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="18"/>
       <name val="Calibri"/>
     </font>
@@ -173,7 +162,6 @@
       <b/>
       <charset val="178"/>
       <family val="2"/>
-      <scheme val="minor"/>
       <sz val="26"/>
       <name val="Calibri"/>
     </font>
@@ -187,43 +175,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor rgb="FF000000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.7999816888943144"/>
+        <fgColor rgb="FFEBF1DE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.5999938962981048"/>
+        <fgColor rgb="FFB9CDE5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.0999786370433668"/>
+        <fgColor rgb="FFDDD9C3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.5999938962981048"/>
+        <fgColor rgb="FFFCD5B5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.7999816888943144"/>
+        <fgColor rgb="FFC6D9F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
